--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-24.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-24.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U12"/>
+  <dimension ref="A1:W15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,6 +534,16 @@
           <t>status</t>
         </is>
       </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>PnL_u</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>PnL_R$</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -613,6 +623,8 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -692,6 +704,8 @@
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -771,6 +785,8 @@
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -780,37 +796,37 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NETHERLANDS 2</t>
+          <t>SPAIN 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Jong FC Utrecht x Heracles</t>
+          <t>Osasuna x Levante</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jong FC Utrecht</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
+          <t>Lay 3x0 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Match Odds (Home)</t>
+          <t>Correct Score (3x0)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -819,20 +835,20 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>6.8</v>
+        <v>23</v>
       </c>
       <c r="K5" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>17.24</v>
+        <v>9.09</v>
       </c>
       <c r="M5" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1x6</t>
+          <t>vs</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -847,9 +863,17 @@
           <t>⏳ PENDENTE</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
+      <c r="S5" t="n">
+        <v>8.77</v>
+      </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -859,37 +883,37 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ENGLAND 1</t>
+          <t>NETHERLANDS 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Fulham x Chelsea</t>
+          <t>Jong FC Utrecht x Heracles</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Jong FC Utrecht</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lay 0x3 Top 3 (Aprovado)</t>
+          <t>Lay Home / DC X2 (Fav Visitante &lt;= 1.65)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Correct Score (0x3)</t>
+          <t>Match Odds (Home)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -898,20 +922,20 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>25</v>
+        <v>6.8</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="L6" t="n">
-        <v>4.17</v>
+        <v>17.24</v>
       </c>
       <c r="M6" t="n">
         <v>100</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2x3</t>
+          <t>1x6</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -929,6 +953,8 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -943,32 +969,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ITALY 3</t>
+          <t>ENGLAND 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Crotone x Foggia</t>
+          <t>Fulham x Chelsea</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lay 2x2 Top 3 (Aprovado)</t>
+          <t>Lay 0x3 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Correct Score (2x2)</t>
+          <t>Correct Score (0x3)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -977,20 +1003,20 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>18.5</v>
+        <v>25</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>5.71</v>
+        <v>4.17</v>
       </c>
       <c r="M7" t="n">
         <v>100</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0x1</t>
+          <t>2x3</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1008,6 +1034,8 @@
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1017,37 +1045,37 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PARAGUAY 1</t>
+          <t>ITALY 3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Libertad x Sportivo San Lorenzo</t>
+          <t>Crotone x Foggia</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sportivo San Lorenzo</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay 2x2 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Correct Score (2x2)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1056,20 +1084,20 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>5.4</v>
+        <v>18.5</v>
       </c>
       <c r="K8" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>22.73</v>
+        <v>5.71</v>
       </c>
       <c r="M8" t="n">
         <v>100</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>1x0</t>
+          <t>0x1</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1087,6 +1115,8 @@
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1096,37 +1126,37 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>COLOMBIA 2</t>
+          <t>PARAGUAY 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Leones FC x Real Cartagena</t>
+          <t>Nacional Asuncion x Sp. Luqueno</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Leones FC</t>
+          <t>Nacional Asuncion</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Real Cartagena</t>
+          <t>Sp. Luqueno</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lay 0x3 Top 3 (Aprovado)</t>
+          <t>Lay 3x0 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Correct Score (0x3)</t>
+          <t>Correct Score (3x0)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1135,37 +1165,47 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>4.35</v>
+        <v>8</v>
       </c>
       <c r="M9" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1x6</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr"/>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr"/>
+          <t>🟢 GREEN</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>7.72</v>
+      </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>0.0386</v>
+      </c>
+      <c r="W9" t="n">
+        <v>7.72</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1175,37 +1215,37 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>COLOMBIA 2</t>
+          <t>PORTUGAL 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Boyaca Patriotas x Atletico FC Cali</t>
+          <t>Gil Vicente x Casa Pia</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Boyaca Patriotas</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Atletico FC Cali</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lay Draw (Fav &lt;= 1.40)</t>
+          <t>Lay 3x0 Top 3 (Aprovado)</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Match Odds (Draw)</t>
+          <t>Correct Score (3x0)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1214,20 +1254,20 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>5.4</v>
+        <v>19</v>
       </c>
       <c r="K10" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>22.73</v>
+        <v>11.11</v>
       </c>
       <c r="M10" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2x0</t>
+          <t>vs</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1242,9 +1282,17 @@
           <t>⏳ PENDENTE</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr"/>
+      <c r="S10" t="n">
+        <v>10.72</v>
+      </c>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1254,37 +1302,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BRAZIL 1</t>
+          <t>PARAGUAY 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Botafogo FR x Athletico-PR</t>
+          <t>Libertad x Sportivo San Lorenzo</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Botafogo FR</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Athletico-PR</t>
+          <t>Sportivo San Lorenzo</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lay 2x2 Top 3 (Aprovado)</t>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Correct Score (2x2)</t>
+          <t>Match Odds (Draw)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1293,20 +1341,20 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>15.5</v>
+        <v>5.4</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="L11" t="n">
-        <v>6.9</v>
+        <v>22.73</v>
       </c>
       <c r="M11" t="n">
         <v>100</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2x3</t>
+          <t>1x0</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1324,6 +1372,8 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1401,6 +1451,251 @@
           <t>LIQUIDADO</t>
         </is>
       </c>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>COLOMBIA 2</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Leones FC x Real Cartagena</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Leones FC</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Real Cartagena</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lay 0x3 Top 3 (Aprovado)</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Correct Score (0x3)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>24</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="M13" t="n">
+        <v>100</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>1x6</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>COLOMBIA 2</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Boyaca Patriotas x Atletico FC Cali</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Boyaca Patriotas</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Atletico FC Cali</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Match Odds (Draw)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="L14" t="n">
+        <v>22.73</v>
+      </c>
+      <c r="M14" t="n">
+        <v>100</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2x0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BRAZIL 1</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Botafogo FR x Athletico-PR</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Botafogo FR</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Athletico-PR</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lay 2x2 Top 3 (Aprovado)</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Correct Score (2x2)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="M15" t="n">
+        <v>100</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2x3</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-24.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-24.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -605,12 +605,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1x0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -686,12 +686,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0x2</t>
+          <t>0-2</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -767,12 +767,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>4x2</t>
+          <t>4-2</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -848,12 +848,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -935,12 +935,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1x6</t>
+          <t>1-6</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -1016,12 +1016,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2x3</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1097,12 +1097,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0x1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1x0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -1514,12 +1514,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1x6</t>
+          <t>1-6</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
@@ -1595,12 +1595,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2x0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
@@ -1676,12 +1676,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2x3</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-24.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-24.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -605,12 +605,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1x0</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -686,12 +686,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0-2</t>
+          <t>0x2</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -767,12 +767,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>4-2</t>
+          <t>4x2</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -848,12 +848,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>vs</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -935,12 +935,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1-6</t>
+          <t>1x6</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -1016,12 +1016,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>2x3</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1097,12 +1097,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>0x1</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>vs</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1x0</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -1514,12 +1514,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1-6</t>
+          <t>1x6</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
@@ -1595,12 +1595,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>2x0</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
@@ -1676,12 +1676,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>2x3</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-24.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-08-24.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sinais_Aprovados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -848,19 +848,19 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>3x0</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>RED</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🔴 RED</t>
         </is>
       </c>
       <c r="S5" t="n">
@@ -1267,19 +1267,19 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>vs</t>
+          <t>1x0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="S10" t="n">
